--- a/Excel/CreateAuctionTestData.xlsx
+++ b/Excel/CreateAuctionTestData.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\doantotnghiep\Unit test\Realtime-Auction-Test\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\doantotnghiep\Unit test\Realtime-Auction-Test\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C41B3D32-D92E-45F0-A005-80FE91AE2A10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20F275AB-0EBF-46A0-85FC-AC9C32FE5FCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12" yWindow="12" windowWidth="23016" windowHeight="12936" xr2:uid="{65F194C7-9389-4FA5-9B7F-7361B7568721}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{65F194C7-9389-4FA5-9B7F-7361B7568721}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="99">
   <si>
     <t>Step_ID</t>
   </si>
@@ -323,9 +323,6 @@
   <si>
     <t>Đồng hồ Rolex Submariner chính hãng Thụy Sĩ phiên bản giới hạn đặc biệt dành cho các quý ông thượng lưu 2026vvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvvv
 v</t>
-  </si>
-  <si>
-    <t>30/06//2026 12:00</t>
   </si>
   <si>
     <t>30/06/2026 12:00</t>
@@ -739,14 +736,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF1EB824-58D2-4724-8D69-31DE1E204955}">
   <dimension ref="A1:L26"/>
-  <sheetFormatPr defaultColWidth="22.44140625" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="22.42578125" defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="10" width="22.44140625" style="2"/>
-    <col min="11" max="11" width="22.44140625" style="6"/>
-    <col min="12" max="16384" width="22.44140625" style="2"/>
+    <col min="1" max="10" width="22.42578125" style="2"/>
+    <col min="11" max="11" width="22.42578125" style="6"/>
+    <col min="12" max="16384" width="22.42578125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="17.399999999999999" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -784,7 +781,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
@@ -820,7 +817,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -858,7 +855,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>17</v>
       </c>
@@ -892,7 +889,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -926,7 +923,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="168.6" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" ht="165.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>23</v>
       </c>
@@ -953,7 +950,7 @@
       </c>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K6" s="7" t="s">
         <v>82</v>
@@ -962,7 +959,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
@@ -996,7 +993,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="286.2" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" ht="264.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>26</v>
       </c>
@@ -1032,7 +1029,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>27</v>
       </c>
@@ -1066,7 +1063,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>30</v>
       </c>
@@ -1102,7 +1099,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>32</v>
       </c>
@@ -1136,7 +1133,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>35</v>
       </c>
@@ -1172,7 +1169,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>37</v>
       </c>
@@ -1208,7 +1205,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>39</v>
       </c>
@@ -1242,7 +1239,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>41</v>
       </c>
@@ -1278,7 +1275,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:12" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>43</v>
       </c>
@@ -1312,7 +1309,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:12" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>46</v>
       </c>
@@ -1348,7 +1345,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:12" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>48</v>
       </c>
@@ -1384,7 +1381,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:12" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>50</v>
       </c>
@@ -1420,7 +1417,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:12" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>53</v>
       </c>
@@ -1456,7 +1453,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:12" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>56</v>
       </c>
@@ -1494,7 +1491,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:12" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>59</v>
       </c>
@@ -1532,7 +1529,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:12" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>61</v>
       </c>
@@ -1566,7 +1563,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:12" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>63</v>
       </c>
@@ -1602,7 +1599,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="34.200000000000003" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:12" ht="33.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>66</v>
       </c>
@@ -1636,7 +1633,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="51" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:12" ht="50.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>69</v>
       </c>
